--- a/rules/CORE-000144/negative/01/data/unit-test-coreid-CG0247-negative.xlsx
+++ b/rules/CORE-000144/negative/01/data/unit-test-coreid-CG0247-negative.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\Verisian\core-contributor\rules\CORE-000144\negative\01\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6ECA975-A26D-4193-923C-5E0C1F89A1D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98E25CF7-FCA7-4C4A-B824-3E4E4EC6C021}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -194,19 +194,23 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -214,7 +218,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -224,11 +228,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
     <fill>
@@ -250,15 +249,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -680,43 +680,43 @@
       </c>
     </row>
     <row r="2" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
+      <c r="A2" s="6">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="7">
-        <v>7</v>
-      </c>
-      <c r="E2" s="7" t="s">
+      <c r="D2" s="6">
+        <v>5</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
-        <v>1</v>
-      </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="D3" s="7">
-        <v>7</v>
-      </c>
-      <c r="E3" s="7" t="s">
+      <c r="D3" s="6">
+        <v>5</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="7" t="s">
-        <v>47</v>
+      <c r="F3" s="4" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -730,7 +730,7 @@
         <v>51</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E4" t="s">
         <v>18</v>
@@ -750,13 +750,13 @@
         <v>51</v>
       </c>
       <c r="D5" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -914,10 +914,10 @@
       <c r="C5" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="5">
         <v>2</v>
       </c>
       <c r="F5" s="4" t="s">
@@ -946,10 +946,10 @@
       <c r="C6" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="5">
         <v>2</v>
       </c>
       <c r="F6" s="4" t="s">
@@ -978,10 +978,10 @@
       <c r="C7" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="7">
         <v>1</v>
       </c>
       <c r="F7" s="4" t="s">
@@ -1010,10 +1010,10 @@
       <c r="C8" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="8">
         <v>2</v>
       </c>
       <c r="F8" s="4" t="s">
